--- a/02_Zero_Shot/outputs/Embedding/BERT-base-uncased/RESULT_pan_bert-base-uncased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/BERT-base-uncased/RESULT_pan_bert-base-uncased_zeroshot.xlsx
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.822578553000312</v>
+        <v>14.38576106600158</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00346948097338152</v>
+        <v>0.01034946839280689</v>
       </c>
     </row>
   </sheetData>
